--- a/__importlar/06-GİDERLER-FATURA-fatura_import_ornek.xlsx
+++ b/__importlar/06-GİDERLER-FATURA-fatura_import_ornek.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehme\Desktop\__importlar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Herd\pymuh\v2\__importlar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D81725-0A46-49D8-B7DE-DC33AE7DFF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7BF7B7-BA3C-45C3-A7FF-86D24CC64167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Açıklama" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="149">
   <si>
     <t>FATURA EXCEL İMPORT REHBERİ</t>
   </si>
@@ -478,6 +478,9 @@
   </si>
   <si>
     <t>ON NUMARA POS -  PEMA POŞET ALIMI</t>
+  </si>
+  <si>
+    <t>Nakit</t>
   </si>
 </sst>
 </file>
@@ -3910,15 +3913,13 @@
       <c r="D67" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E67" s="4" t="str">
-        <f t="shared" ref="E67:E130" si="4">IF(F67="Nakit","","MEHMET DAŞDEMİR - K.K.")</f>
-        <v>MEHMET DAŞDEMİR - K.K.</v>
-      </c>
-      <c r="F67" t="str">
-        <f t="shared" ref="F67:F130" si="5">IF(G67="TL KASA","Nakit","Vadeli")</f>
-        <v>Vadeli</v>
-      </c>
-      <c r="G67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" t="s">
+        <v>148</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="H67" t="s">
         <v>33</v>
       </c>
@@ -3935,11 +3936,11 @@
         <v>0</v>
       </c>
       <c r="N67" t="str">
-        <f t="shared" ref="N67:N130" si="6">IF(G67="NAKİT", "Kasa", IF(G67="K.K.", "Banka", ""))</f>
+        <f t="shared" ref="N67:N130" si="4">IF(G67="NAKİT", "Kasa", IF(G67="K.K.", "Banka", ""))</f>
         <v/>
       </c>
       <c r="O67" t="str">
-        <f t="shared" ref="O67:O130" si="7">IF(N67="Kasa", "TL KASA", IF(N67="Banka", "MEHMET DAŞDEMİR - K.K.", ""))</f>
+        <f t="shared" ref="O67:O130" si="5">IF(N67="Kasa", "TL KASA", IF(N67="Banka", "MEHMET DAŞDEMİR - K.K.", ""))</f>
         <v/>
       </c>
     </row>
@@ -3954,11 +3955,11 @@
         <v>100</v>
       </c>
       <c r="E68" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E67:E130" si="6">IF(F68="Nakit","","MEHMET DAŞDEMİR - K.K.")</f>
         <v/>
       </c>
       <c r="F68" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="F67:F130" si="7">IF(G68="TL KASA","Nakit","Vadeli")</f>
         <v>Nakit</v>
       </c>
       <c r="G68" s="4" t="s">
@@ -3980,11 +3981,11 @@
         <v>0</v>
       </c>
       <c r="N68" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O68" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3999,11 +4000,11 @@
         <v>101</v>
       </c>
       <c r="E69" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F69" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G69" s="4" t="s">
@@ -4025,11 +4026,11 @@
         <v>0</v>
       </c>
       <c r="N69" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O69" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4044,11 +4045,11 @@
         <v>102</v>
       </c>
       <c r="E70" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F70" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G70" s="4" t="s">
@@ -4070,11 +4071,11 @@
         <v>0</v>
       </c>
       <c r="N70" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O70" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4089,11 +4090,11 @@
         <v>88</v>
       </c>
       <c r="E71" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F71" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G71" s="4" t="s">
@@ -4115,11 +4116,11 @@
         <v>0</v>
       </c>
       <c r="N71" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O71" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4134,11 +4135,11 @@
         <v>103</v>
       </c>
       <c r="E72" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F72" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G72" s="4" t="s">
@@ -4160,11 +4161,11 @@
         <v>0</v>
       </c>
       <c r="N72" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O72" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4179,11 +4180,11 @@
         <v>84</v>
       </c>
       <c r="E73" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F73" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G73" s="4" t="s">
@@ -4205,11 +4206,11 @@
         <v>0</v>
       </c>
       <c r="N73" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O73" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4224,11 +4225,11 @@
         <v>101</v>
       </c>
       <c r="E74" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G74" s="4" t="s">
@@ -4250,11 +4251,11 @@
         <v>0</v>
       </c>
       <c r="N74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4269,11 +4270,11 @@
         <v>104</v>
       </c>
       <c r="E75" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F75" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G75" s="4" t="s">
@@ -4295,11 +4296,11 @@
         <v>0</v>
       </c>
       <c r="N75" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O75" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4314,11 +4315,11 @@
         <v>88</v>
       </c>
       <c r="E76" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F76" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G76" s="4" t="s">
@@ -4340,11 +4341,11 @@
         <v>0</v>
       </c>
       <c r="N76" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O76" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4359,11 +4360,11 @@
         <v>105</v>
       </c>
       <c r="E77" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G77" s="4" t="s">
@@ -4385,11 +4386,11 @@
         <v>0</v>
       </c>
       <c r="N77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O77" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4404,11 +4405,11 @@
         <v>97</v>
       </c>
       <c r="E78" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>MEHMET DAŞDEMİR - K.K.</v>
       </c>
       <c r="F78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Vadeli</v>
       </c>
       <c r="G78" s="4"/>
@@ -4428,11 +4429,11 @@
         <v>0</v>
       </c>
       <c r="N78" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O78" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4447,11 +4448,11 @@
         <v>106</v>
       </c>
       <c r="E79" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F79" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G79" s="4" t="s">
@@ -4473,11 +4474,11 @@
         <v>0</v>
       </c>
       <c r="N79" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O79" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4492,11 +4493,11 @@
         <v>107</v>
       </c>
       <c r="E80" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G80" s="4" t="s">
@@ -4518,11 +4519,11 @@
         <v>0</v>
       </c>
       <c r="N80" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O80" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4537,11 +4538,11 @@
         <v>108</v>
       </c>
       <c r="E81" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F81" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G81" s="4" t="s">
@@ -4563,11 +4564,11 @@
         <v>0</v>
       </c>
       <c r="N81" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O81" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4582,11 +4583,11 @@
         <v>109</v>
       </c>
       <c r="E82" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>MEHMET DAŞDEMİR - K.K.</v>
       </c>
       <c r="F82" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Vadeli</v>
       </c>
       <c r="G82" s="4"/>
@@ -4606,11 +4607,11 @@
         <v>0</v>
       </c>
       <c r="N82" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O82" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4625,11 +4626,11 @@
         <v>110</v>
       </c>
       <c r="E83" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F83" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G83" s="4" t="s">
@@ -4651,11 +4652,11 @@
         <v>0</v>
       </c>
       <c r="N83" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O83" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4670,11 +4671,11 @@
         <v>101</v>
       </c>
       <c r="E84" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F84" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G84" s="4" t="s">
@@ -4696,11 +4697,11 @@
         <v>0</v>
       </c>
       <c r="N84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4715,11 +4716,11 @@
         <v>111</v>
       </c>
       <c r="E85" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F85" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G85" s="4" t="s">
@@ -4741,11 +4742,11 @@
         <v>0</v>
       </c>
       <c r="N85" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O85" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4760,11 +4761,11 @@
         <v>112</v>
       </c>
       <c r="E86" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F86" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G86" s="4" t="s">
@@ -4786,11 +4787,11 @@
         <v>0</v>
       </c>
       <c r="N86" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O86" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4805,11 +4806,11 @@
         <v>113</v>
       </c>
       <c r="E87" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G87" s="4" t="s">
@@ -4831,11 +4832,11 @@
         <v>0</v>
       </c>
       <c r="N87" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4850,11 +4851,11 @@
         <v>114</v>
       </c>
       <c r="E88" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>MEHMET DAŞDEMİR - K.K.</v>
       </c>
       <c r="F88" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Vadeli</v>
       </c>
       <c r="G88" s="4"/>
@@ -4874,11 +4875,11 @@
         <v>0</v>
       </c>
       <c r="N88" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O88" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4893,11 +4894,11 @@
         <v>115</v>
       </c>
       <c r="E89" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>MEHMET DAŞDEMİR - K.K.</v>
       </c>
       <c r="F89" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Vadeli</v>
       </c>
       <c r="G89" s="4"/>
@@ -4917,11 +4918,11 @@
         <v>0</v>
       </c>
       <c r="N89" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O89" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4936,11 +4937,11 @@
         <v>116</v>
       </c>
       <c r="E90" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F90" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G90" s="4" t="s">
@@ -4962,11 +4963,11 @@
         <v>0</v>
       </c>
       <c r="N90" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O90" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4981,11 +4982,11 @@
         <v>117</v>
       </c>
       <c r="E91" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F91" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G91" s="4" t="s">
@@ -5007,11 +5008,11 @@
         <v>0</v>
       </c>
       <c r="N91" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O91" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5026,11 +5027,11 @@
         <v>107</v>
       </c>
       <c r="E92" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F92" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G92" s="4" t="s">
@@ -5052,11 +5053,11 @@
         <v>0</v>
       </c>
       <c r="N92" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O92" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5071,11 +5072,11 @@
         <v>118</v>
       </c>
       <c r="E93" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F93" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G93" s="4" t="s">
@@ -5097,11 +5098,11 @@
         <v>0</v>
       </c>
       <c r="N93" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O93" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5116,11 +5117,11 @@
         <v>119</v>
       </c>
       <c r="E94" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F94" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G94" s="4" t="s">
@@ -5142,11 +5143,11 @@
         <v>0</v>
       </c>
       <c r="N94" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O94" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5161,11 +5162,11 @@
         <v>120</v>
       </c>
       <c r="E95" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F95" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G95" s="4" t="s">
@@ -5187,11 +5188,11 @@
         <v>0</v>
       </c>
       <c r="N95" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O95" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5206,11 +5207,11 @@
         <v>121</v>
       </c>
       <c r="E96" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F96" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G96" s="4" t="s">
@@ -5232,11 +5233,11 @@
         <v>0</v>
       </c>
       <c r="N96" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O96" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5251,11 +5252,11 @@
         <v>122</v>
       </c>
       <c r="E97" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F97" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G97" s="4" t="s">
@@ -5277,11 +5278,11 @@
         <v>0</v>
       </c>
       <c r="N97" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O97" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5296,11 +5297,11 @@
         <v>123</v>
       </c>
       <c r="E98" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F98" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G98" s="4" t="s">
@@ -5322,11 +5323,11 @@
         <v>0</v>
       </c>
       <c r="N98" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O98" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5341,11 +5342,11 @@
         <v>124</v>
       </c>
       <c r="E99" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F99" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G99" s="4" t="s">
@@ -5367,11 +5368,11 @@
         <v>0</v>
       </c>
       <c r="N99" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O99" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5386,11 +5387,11 @@
         <v>101</v>
       </c>
       <c r="E100" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F100" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G100" s="4" t="s">
@@ -5412,11 +5413,11 @@
         <v>0</v>
       </c>
       <c r="N100" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O100" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5431,11 +5432,11 @@
         <v>125</v>
       </c>
       <c r="E101" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F101" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G101" s="4" t="s">
@@ -5457,11 +5458,11 @@
         <v>0</v>
       </c>
       <c r="N101" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O101" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5476,11 +5477,11 @@
         <v>126</v>
       </c>
       <c r="E102" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F102" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G102" s="4" t="s">
@@ -5502,11 +5503,11 @@
         <v>0</v>
       </c>
       <c r="N102" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O102" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5521,11 +5522,11 @@
         <v>127</v>
       </c>
       <c r="E103" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F103" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G103" s="4" t="s">
@@ -5547,11 +5548,11 @@
         <v>0</v>
       </c>
       <c r="N103" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O103" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5566,11 +5567,11 @@
         <v>128</v>
       </c>
       <c r="E104" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F104" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G104" s="4" t="s">
@@ -5592,11 +5593,11 @@
         <v>0</v>
       </c>
       <c r="N104" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O104" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5611,11 +5612,11 @@
         <v>129</v>
       </c>
       <c r="E105" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F105" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G105" s="4" t="s">
@@ -5637,11 +5638,11 @@
         <v>0</v>
       </c>
       <c r="N105" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O105" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5656,11 +5657,11 @@
         <v>130</v>
       </c>
       <c r="E106" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F106" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G106" s="4" t="s">
@@ -5682,11 +5683,11 @@
         <v>0</v>
       </c>
       <c r="N106" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O106" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5701,11 +5702,11 @@
         <v>131</v>
       </c>
       <c r="E107" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>MEHMET DAŞDEMİR - K.K.</v>
       </c>
       <c r="F107" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Vadeli</v>
       </c>
       <c r="G107" s="4"/>
@@ -5725,11 +5726,11 @@
         <v>0</v>
       </c>
       <c r="N107" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O107" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5744,11 +5745,11 @@
         <v>113</v>
       </c>
       <c r="E108" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F108" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G108" s="4" t="s">
@@ -5770,11 +5771,11 @@
         <v>0</v>
       </c>
       <c r="N108" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O108" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5789,11 +5790,11 @@
         <v>132</v>
       </c>
       <c r="E109" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F109" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G109" s="4" t="s">
@@ -5815,11 +5816,11 @@
         <v>0</v>
       </c>
       <c r="N109" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O109" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5834,11 +5835,11 @@
         <v>132</v>
       </c>
       <c r="E110" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F110" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G110" s="4" t="s">
@@ -5860,11 +5861,11 @@
         <v>0</v>
       </c>
       <c r="N110" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O110" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5879,11 +5880,11 @@
         <v>133</v>
       </c>
       <c r="E111" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F111" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G111" s="4" t="s">
@@ -5905,11 +5906,11 @@
         <v>0</v>
       </c>
       <c r="N111" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5924,11 +5925,11 @@
         <v>134</v>
       </c>
       <c r="E112" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>MEHMET DAŞDEMİR - K.K.</v>
       </c>
       <c r="F112" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Vadeli</v>
       </c>
       <c r="G112" s="4"/>
@@ -5948,11 +5949,11 @@
         <v>0</v>
       </c>
       <c r="N112" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O112" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5967,11 +5968,11 @@
         <v>135</v>
       </c>
       <c r="E113" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F113" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G113" s="4" t="s">
@@ -5993,11 +5994,11 @@
         <v>0</v>
       </c>
       <c r="N113" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O113" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6012,11 +6013,11 @@
         <v>101</v>
       </c>
       <c r="E114" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F114" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G114" s="4" t="s">
@@ -6038,11 +6039,11 @@
         <v>0</v>
       </c>
       <c r="N114" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O114" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6057,11 +6058,11 @@
         <v>101</v>
       </c>
       <c r="E115" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F115" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G115" s="4" t="s">
@@ -6083,11 +6084,11 @@
         <v>0</v>
       </c>
       <c r="N115" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O115" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6102,11 +6103,11 @@
         <v>136</v>
       </c>
       <c r="E116" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F116" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G116" s="4" t="s">
@@ -6128,11 +6129,11 @@
         <v>0</v>
       </c>
       <c r="N116" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O116" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6147,11 +6148,11 @@
         <v>137</v>
       </c>
       <c r="E117" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F117" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G117" s="4" t="s">
@@ -6173,11 +6174,11 @@
         <v>0</v>
       </c>
       <c r="N117" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O117" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6192,11 +6193,11 @@
         <v>138</v>
       </c>
       <c r="E118" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F118" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G118" s="4" t="s">
@@ -6218,11 +6219,11 @@
         <v>0</v>
       </c>
       <c r="N118" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O118" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6237,11 +6238,11 @@
         <v>138</v>
       </c>
       <c r="E119" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F119" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G119" s="4" t="s">
@@ -6263,11 +6264,11 @@
         <v>0</v>
       </c>
       <c r="N119" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O119" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6282,11 +6283,11 @@
         <v>101</v>
       </c>
       <c r="E120" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F120" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G120" s="4" t="s">
@@ -6308,11 +6309,11 @@
         <v>0</v>
       </c>
       <c r="N120" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O120" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6327,11 +6328,11 @@
         <v>139</v>
       </c>
       <c r="E121" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F121" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G121" s="4" t="s">
@@ -6353,11 +6354,11 @@
         <v>0</v>
       </c>
       <c r="N121" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O121" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6372,11 +6373,11 @@
         <v>140</v>
       </c>
       <c r="E122" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G122" s="4" t="s">
@@ -6398,11 +6399,11 @@
         <v>0</v>
       </c>
       <c r="N122" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O122" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6417,11 +6418,11 @@
         <v>141</v>
       </c>
       <c r="E123" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F123" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G123" s="4" t="s">
@@ -6443,11 +6444,11 @@
         <v>0</v>
       </c>
       <c r="N123" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O123" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6462,11 +6463,11 @@
         <v>137</v>
       </c>
       <c r="E124" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F124" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G124" s="4" t="s">
@@ -6488,11 +6489,11 @@
         <v>0</v>
       </c>
       <c r="N124" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O124" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6507,11 +6508,11 @@
         <v>142</v>
       </c>
       <c r="E125" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F125" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G125" s="4" t="s">
@@ -6533,11 +6534,11 @@
         <v>0</v>
       </c>
       <c r="N125" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O125" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6552,11 +6553,11 @@
         <v>143</v>
       </c>
       <c r="E126" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G126" s="4" t="s">
@@ -6578,11 +6579,11 @@
         <v>0</v>
       </c>
       <c r="N126" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O126" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6597,11 +6598,11 @@
         <v>101</v>
       </c>
       <c r="E127" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F127" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G127" s="4" t="s">
@@ -6623,11 +6624,11 @@
         <v>0</v>
       </c>
       <c r="N127" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O127" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6642,11 +6643,11 @@
         <v>139</v>
       </c>
       <c r="E128" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F128" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G128" s="4" t="s">
@@ -6668,11 +6669,11 @@
         <v>0</v>
       </c>
       <c r="N128" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O128" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6687,11 +6688,11 @@
         <v>144</v>
       </c>
       <c r="E129" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F129" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G129" s="4" t="s">
@@ -6713,11 +6714,11 @@
         <v>0</v>
       </c>
       <c r="N129" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O129" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6732,11 +6733,11 @@
         <v>144</v>
       </c>
       <c r="E130" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="F130" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Nakit</v>
       </c>
       <c r="G130" s="4" t="s">
@@ -6758,11 +6759,11 @@
         <v>0</v>
       </c>
       <c r="N130" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O130" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
